--- a/artfynd/A 20831-2024 artfynd.xlsx
+++ b/artfynd/A 20831-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127049035</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127049033</v>
       </c>
       <c r="B4" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20831-2024 artfynd.xlsx
+++ b/artfynd/A 20831-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127049035</v>
       </c>
       <c r="B3" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127049033</v>
       </c>
       <c r="B4" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20831-2024 artfynd.xlsx
+++ b/artfynd/A 20831-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127049035</v>
       </c>
       <c r="B3" t="n">
-        <v>98420</v>
+        <v>98421</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127049033</v>
       </c>
       <c r="B4" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20831-2024 artfynd.xlsx
+++ b/artfynd/A 20831-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127049035</v>
       </c>
       <c r="B3" t="n">
-        <v>98421</v>
+        <v>98425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127049033</v>
       </c>
       <c r="B4" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20831-2024 artfynd.xlsx
+++ b/artfynd/A 20831-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127049035</v>
       </c>
       <c r="B3" t="n">
-        <v>98425</v>
+        <v>98426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127049033</v>
       </c>
       <c r="B4" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20831-2024 artfynd.xlsx
+++ b/artfynd/A 20831-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127049035</v>
       </c>
       <c r="B3" t="n">
-        <v>98426</v>
+        <v>98428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127049033</v>
       </c>
       <c r="B4" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20831-2024 artfynd.xlsx
+++ b/artfynd/A 20831-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127049035</v>
       </c>
       <c r="B3" t="n">
-        <v>98428</v>
+        <v>98434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127049033</v>
       </c>
       <c r="B4" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20831-2024 artfynd.xlsx
+++ b/artfynd/A 20831-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>127049035</v>
       </c>
       <c r="B3" t="n">
-        <v>98434</v>
+        <v>98414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>127049033</v>
       </c>
       <c r="B4" t="n">
-        <v>109283</v>
+        <v>109260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20831-2024 artfynd.xlsx
+++ b/artfynd/A 20831-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118273662</v>
+        <v>16849876</v>
       </c>
       <c r="B2" t="n">
-        <v>42955</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101242</v>
+        <v>2015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Vit taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Hydnum albidum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>Peck</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hambrars naturreservat (Hambrars naturreservat), Gtl</t>
+          <t>Hajden, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720078</v>
+        <v>720047</v>
       </c>
       <c r="R2" t="n">
-        <v>6369705</v>
+        <v>6369600</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2014-10-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2014-10-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,75 +756,67 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Ingrid Thomasson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127049035</v>
+        <v>118273662</v>
       </c>
       <c r="B3" t="n">
-        <v>98434</v>
+        <v>43467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+          <t>Hambrars naturreservat, Hambrars naturreservat, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720027</v>
+        <v>720078</v>
       </c>
       <c r="R3" t="n">
-        <v>6369608</v>
+        <v>6369705</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +840,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,66 +856,70 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med enbuskar.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127049033</v>
+        <v>127049018</v>
       </c>
       <c r="B4" t="n">
-        <v>109283</v>
+        <v>99096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720050</v>
+        <v>720098</v>
       </c>
       <c r="R4" t="n">
-        <v>6369636</v>
+        <v>6369601</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,6 +980,1156 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127049035</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>720027</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6369608</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127049019</v>
+      </c>
+      <c r="B6" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>720098</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6369601</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127049011</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>720068</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6369585</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127049014</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>720103</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6369589</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127049048</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38., Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>719973</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6369602</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Även med blekgul blomma. Skogskant NO körväg. A 20831-2024.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Torräng vid körväg.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127049033</v>
+      </c>
+      <c r="B10" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>720050</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6369636</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127049012</v>
+      </c>
+      <c r="B11" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>720068</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6369585</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127049015</v>
+      </c>
+      <c r="B12" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>720103</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6369589</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127049049</v>
+      </c>
+      <c r="B13" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38., Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>719973</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6369602</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Skogskant NO körväg. A 20831-2024.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Torräng vid körväg.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127049009</v>
+      </c>
+      <c r="B14" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>720068</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6369585</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127049013</v>
+      </c>
+      <c r="B15" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>720103</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6369589</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20831-2024 artfynd.xlsx
+++ b/artfynd/A 20831-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -872,57 +872,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127049018</v>
+        <v>134659109</v>
       </c>
       <c r="B4" t="n">
-        <v>99096</v>
+        <v>43472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720098</v>
+        <v>720085</v>
       </c>
       <c r="R4" t="n">
-        <v>6369601</v>
+        <v>6369652</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -946,12 +937,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -962,78 +968,64 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med enbuskar.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127049035</v>
+        <v>134659110</v>
       </c>
       <c r="B5" t="n">
-        <v>99096</v>
+        <v>43472</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720027</v>
+        <v>720087</v>
       </c>
       <c r="R5" t="n">
-        <v>6369608</v>
+        <v>6369651</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1057,12 +1049,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,31 +1075,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med enbuskar.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127049019</v>
+        <v>134659113</v>
       </c>
       <c r="B6" t="n">
-        <v>108116</v>
+        <v>43472</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,46 +1102,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220079</v>
+        <v>101242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720098</v>
+        <v>720089</v>
       </c>
       <c r="R6" t="n">
-        <v>6369601</v>
+        <v>6369676</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,12 +1156,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,31 +1187,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med enbuskar.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127049011</v>
+        <v>134659114</v>
       </c>
       <c r="B7" t="n">
-        <v>104640</v>
+        <v>43472</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,37 +1214,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220164</v>
+        <v>101242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720068</v>
+        <v>720091</v>
       </c>
       <c r="R7" t="n">
-        <v>6369585</v>
+        <v>6369679</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1270,12 +1268,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1286,31 +1299,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Kalkglänta.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127049014</v>
+        <v>134659115</v>
       </c>
       <c r="B8" t="n">
-        <v>104640</v>
+        <v>43472</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,34 +1326,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220164</v>
+        <v>101242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720103</v>
+        <v>720097</v>
       </c>
       <c r="R8" t="n">
-        <v>6369589</v>
+        <v>6369714</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1372,12 +1380,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,31 +1406,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Kalkglänta.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127049048</v>
+        <v>134659116</v>
       </c>
       <c r="B9" t="n">
-        <v>104640</v>
+        <v>43472</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,37 +1433,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220164</v>
+        <v>101242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38., Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>719973</v>
+        <v>720118</v>
       </c>
       <c r="R9" t="n">
-        <v>6369602</v>
+        <v>6369742</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1474,17 +1487,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Även med blekgul blomma. Skogskant NO körväg. A 20831-2024.</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1495,31 +1513,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Torräng vid körväg.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127049033</v>
+        <v>134659118</v>
       </c>
       <c r="B10" t="n">
-        <v>110078</v>
+        <v>43472</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,37 +1540,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720050</v>
+        <v>720057</v>
       </c>
       <c r="R10" t="n">
-        <v>6369636</v>
+        <v>6369721</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1581,12 +1594,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1597,31 +1620,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog med enbuskar.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127049012</v>
+        <v>134659119</v>
       </c>
       <c r="B11" t="n">
-        <v>107517</v>
+        <v>43472</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1629,34 +1647,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720068</v>
+        <v>720040</v>
       </c>
       <c r="R11" t="n">
-        <v>6369585</v>
+        <v>6369710</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1683,12 +1701,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1699,31 +1732,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Kalkglänta.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127049015</v>
+        <v>134659120</v>
       </c>
       <c r="B12" t="n">
-        <v>107517</v>
+        <v>43472</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1731,37 +1759,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720103</v>
+        <v>720060</v>
       </c>
       <c r="R12" t="n">
-        <v>6369589</v>
+        <v>6369707</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1785,12 +1813,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1801,31 +1844,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Kalkglänta.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127049049</v>
+        <v>134659365</v>
       </c>
       <c r="B13" t="n">
-        <v>107517</v>
+        <v>43472</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,37 +1871,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38., Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>719973</v>
+        <v>720042</v>
       </c>
       <c r="R13" t="n">
-        <v>6369602</v>
+        <v>6369667</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1887,17 +1925,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Skogskant NO körväg. A 20831-2024.</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1908,31 +1956,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Torräng vid körväg.</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127049009</v>
+        <v>134659367</v>
       </c>
       <c r="B14" t="n">
-        <v>107061</v>
+        <v>43472</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,34 +1983,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221903</v>
+        <v>101242</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720068</v>
+        <v>720030</v>
       </c>
       <c r="R14" t="n">
-        <v>6369585</v>
+        <v>6369671</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1994,12 +2037,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2010,31 +2068,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Kalkglänta.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127049013</v>
+        <v>134659368</v>
       </c>
       <c r="B15" t="n">
-        <v>107061</v>
+        <v>43472</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,34 +2095,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221903</v>
+        <v>101242</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720103</v>
+        <v>720038</v>
       </c>
       <c r="R15" t="n">
-        <v>6369589</v>
+        <v>6369645</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2096,12 +2149,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1st</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2112,24 +2180,2064 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Kalkglänta.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134659369</v>
+      </c>
+      <c r="B16" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ala Lauritse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>720012</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6369669</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134659370</v>
+      </c>
+      <c r="B17" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ala Lauritse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>720005</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6369673</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134659371</v>
+      </c>
+      <c r="B18" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ala Lauritse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>720065</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6369693</v>
+      </c>
+      <c r="S18" t="n">
+        <v>11</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2st parar sig</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134659374</v>
+      </c>
+      <c r="B19" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ala Lauritse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>720076</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6369687</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>3st</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134659375</v>
+      </c>
+      <c r="B20" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ala Lauritse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>720105</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6369715</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134659376</v>
+      </c>
+      <c r="B21" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ala Lauritse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>720074</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6369729</v>
+      </c>
+      <c r="S21" t="n">
+        <v>12</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134659378</v>
+      </c>
+      <c r="B22" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ala Lauritse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>720070</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6369747</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127049018</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>720098</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6369601</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127049035</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>720027</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6369608</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127049019</v>
+      </c>
+      <c r="B25" t="n">
+        <v>108116</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>720098</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6369601</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127049011</v>
+      </c>
+      <c r="B26" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>720068</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6369585</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127049014</v>
+      </c>
+      <c r="B27" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>720103</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6369589</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127049048</v>
+      </c>
+      <c r="B28" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38., Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>719973</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6369602</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Även med blekgul blomma. Skogskant NO körväg. A 20831-2024.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Torräng vid körväg.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127049033</v>
+      </c>
+      <c r="B29" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>720050</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6369636</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog med enbuskar.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127049012</v>
+      </c>
+      <c r="B30" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>720068</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6369585</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127049015</v>
+      </c>
+      <c r="B31" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>720103</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6369589</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127049049</v>
+      </c>
+      <c r="B32" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38., Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>719973</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6369602</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Skogskant NO körväg. A 20831-2024.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Torräng vid körväg.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127049009</v>
+      </c>
+      <c r="B33" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>720068</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6369585</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127049013</v>
+      </c>
+      <c r="B34" t="n">
+        <v>107061</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221903</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Axveronika</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Veronica spicata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38.A 20831-2024., Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>720103</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6369589</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkglänta.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20831-2024 artfynd.xlsx
+++ b/artfynd/A 20831-2024 artfynd.xlsx
@@ -1960,12 +1960,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2072,12 +2072,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2184,12 +2184,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2296,12 +2296,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2408,12 +2408,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2520,12 +2520,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2632,12 +2632,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2744,12 +2744,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2856,12 +2856,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2968,12 +2968,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 20831-2024 artfynd.xlsx
+++ b/artfynd/A 20831-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -772,6 +777,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16849876</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -869,6 +879,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118273662</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659109</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659110</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1200,6 +1225,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659113</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659114</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659115</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1526,6 +1566,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659116</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1633,6 +1678,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659118</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1745,6 +1795,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659119</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1857,6 +1912,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659120</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1969,6 +2029,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659365</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2081,6 +2146,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659367</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2193,6 +2263,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659368</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2305,6 +2380,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659369</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2417,6 +2497,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659370</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2529,6 +2614,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659371</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2641,6 +2731,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659374</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2753,6 +2848,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659375</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2865,6 +2965,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659376</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2977,6 +3082,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659378</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3088,6 +3198,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049018</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3199,6 +3314,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049035</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3310,6 +3430,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049019</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3412,6 +3537,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049011</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3514,6 +3644,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049014</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3621,6 +3756,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049048</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3723,6 +3863,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049033</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3825,6 +3970,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049012</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3927,6 +4077,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049015</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4034,6 +4189,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049049</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4136,6 +4296,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049009</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4238,8 +4403,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127049013</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>